--- a/data/merged/2026-10-08/MERGED_IT_Spot-Cleaner_2026-10-08.xlsx
+++ b/data/merged/2026-10-08/MERGED_IT_Spot-Cleaner_2026-10-08.xlsx
@@ -7053,94 +7053,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Product 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7466,7 +7378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -17819,40 +17731,40 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0753NXDPR</t>
+          <t>B0H3KVMBCH</t>
         </is>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>Bissell</t>
+          <t>MELLWIN</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/BISSELL/page/EDA95B6C-7064-466B-BACA-347C73A9A423?lp_asin=B0753NXDPR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=MELLWIN</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Oxygen Boost Potenziatore Detergente 1 L 1134NsPer formule detergenti per pulitori portatili SpotClean, per moquett</t>
+          <t>MELLWIN lava tappezzeria vapore e riscaldamento,18 kPa,Riscaldamento rapidospulitore tappezzeria da 1250 W Proprietari di a</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0753NXDPR?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H3KVMBCH?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51L21EY2IeL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71J+7Vw8QSL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0753NXDPR</t>
+          <t>B0H3KVMBCH</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
@@ -17866,84 +17778,74 @@
         </is>
       </c>
       <c r="O46" s="15">
-        <v>3343</v>
+        <v>59098</v>
       </c>
       <c r="P46" s="15">
-        <v>-938</v>
+        <v>97860</v>
       </c>
       <c r="Q46" s="16">
-        <v>-0.39</v>
+        <v>0.62</v>
       </c>
       <c r="R46" s="17" t="inlineStr">
         <is>
-          <t>Lavatappeti
-Detergenti e prodotti per la pulizia</t>
+          <t>Lavatappeti</t>
         </is>
       </c>
       <c r="S46" s="18" t="inlineStr">
         <is>
-          <t>12
-409</t>
+          <t>50</t>
         </is>
       </c>
       <c r="T46" s="15">
-        <v>343</v>
+        <v>37</v>
       </c>
       <c r="U46" s="16">
-        <v>0.03</v>
+        <v>2.57</v>
       </c>
       <c r="V46" s="15">
-        <v>5142</v>
-      </c>
-      <c r="W46" s="15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="X46" s="15">
-        <v>1499</v>
-      </c>
+        <v>3885</v>
+      </c>
+      <c r="W46" s="15"/>
+      <c r="X46" s="15"/>
       <c r="Y46" s="19">
         <v>1</v>
       </c>
       <c r="Z46" s="20">
-        <v>14.99</v>
+        <v>104.99</v>
       </c>
       <c r="AA46"/>
       <c r="AB46"/>
-      <c r="AC46" s="15">
-        <v>20</v>
-      </c>
+      <c r="AC46" s="15"/>
       <c r="AD46" s="19">
-        <v>9440</v>
+        <v>15</v>
       </c>
       <c r="AE46" s="15">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="AF46" s="21">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="AG46" s="22">
-        <v>0.242</v>
+        <v>0.3514</v>
       </c>
       <c r="AH46" s="20">
-        <v>5.19</v>
+        <v>5.46</v>
       </c>
       <c r="AI46" s="16">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AJ46"/>
       <c r="AK46" s="13" t="inlineStr">
         <is>
-          <t>2017-10-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AL46" s="19">
-        <v>3288</v>
+        <v>61</v>
       </c>
       <c r="AM46" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN46" s="13"/>
@@ -17953,27 +17855,35 @@
         <v>10</v>
       </c>
       <c r="AR46" s="19">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AS46" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>EUROAPEX LANDING</t>
         </is>
       </c>
       <c r="AT46" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU46" s="13"/>
-      <c r="AV46" s="14"/>
-      <c r="AW46" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU46" s="13" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="AV46" s="14" t="inlineStr">
+        <is>
+          <t>DOLNOŚLĄSKIE 53-332 PL</t>
+        </is>
+      </c>
+      <c r="AW46" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ABSTVEQNNON26</t>
+        </is>
+      </c>
       <c r="AX46" s="13"/>
-      <c r="AY46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY46" s="13"/>
       <c r="AZ46" s="13"/>
       <c r="BA46" s="13"/>
       <c r="BB46" s="13"/>
@@ -17991,54 +17901,50 @@
       <c r="BF46" s="13"/>
       <c r="BG46" s="13"/>
       <c r="BH46" s="14"/>
-      <c r="BI46" s="23" t="inlineStr">
-        <is>
-          <t>Scelta Amazon</t>
-        </is>
-      </c>
+      <c r="BI46" s="23"/>
       <c r="BJ46" s="23" t="inlineStr">
         <is>
-          <t>1.1 kg</t>
+          <t>4 kg</t>
         </is>
       </c>
       <c r="BK46" s="23" t="inlineStr">
         <is>
-          <t>1.10 kg</t>
+          <t>4.00 kg</t>
         </is>
       </c>
       <c r="BL46" s="23" t="inlineStr">
         <is>
-          <t>7 x 12 x 23.8 cm</t>
+          <t>43 x 19 x 32 cm</t>
         </is>
       </c>
       <c r="BM46" s="23" t="inlineStr">
         <is>
-          <t>7.00 x 12.00 x 23.80 cm</t>
+          <t>43.00 x 19.00 x 32.00 cm</t>
         </is>
       </c>
       <c r="BN46" s="23" t="inlineStr">
         <is>
-          <t>1.1 kg</t>
+          <t>4.67 kg</t>
         </is>
       </c>
       <c r="BO46" s="23" t="inlineStr">
         <is>
-          <t>1.10 kg</t>
+          <t>4.67 kg</t>
         </is>
       </c>
       <c r="BP46" s="23" t="inlineStr">
         <is>
-          <t>23.5 x 11.9 x 6.9 cm</t>
+          <t>45 x 31.5 x 19.9 cm</t>
         </is>
       </c>
       <c r="BQ46" s="23" t="inlineStr">
         <is>
-          <t>23.50 x 11.90 x 6.90 cm</t>
+          <t>45.00 x 31.50 x 19.90 cm</t>
         </is>
       </c>
       <c r="BR46" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -18049,40 +17955,40 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0H3KVMBCH</t>
+          <t>B0D8KZDB13</t>
         </is>
       </c>
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>MELLWIN</t>
+          <t>WORKPRO</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=MELLWIN</t>
+          <t>https://www.amazon.it/stores/WORKPROCuraOgniDettaglioperLei/page/3671C642-31F6-4DBC-ACA3-01D7F4B6F085?lp_asin=B0D8KZDB13&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>MELLWIN lava tappezzeria vapore e riscaldamento,18 kPa,Riscaldamento rapidospulitore tappezzeria da 1250 W Proprietari di a</t>
+          <t>WORKPRO Lavatappeti Portatile 450W, Lava Tappezzeria, Pulitore Tappezzeria, Ideale per Pulisci Scale, Divano, Sedili Auto, Mo</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0H3KVMBCH?psc=1</t>
+          <t>https://www.amazon.it/dp/B0D8KZDB13?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71J+7Vw8QSL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41preSMoUJL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0H3KVMBCH</t>
+          <t>B0D8KZDB13</t>
         </is>
       </c>
       <c r="M47" s="14" t="inlineStr">
@@ -18096,13 +18002,13 @@
         </is>
       </c>
       <c r="O47" s="15">
-        <v>59098</v>
+        <v>45732</v>
       </c>
       <c r="P47" s="15">
-        <v>97860</v>
+        <v>243255</v>
       </c>
       <c r="Q47" s="16">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="R47" s="17" t="inlineStr">
         <is>
@@ -18111,17 +18017,17 @@
       </c>
       <c r="S47" s="18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>45</t>
         </is>
       </c>
       <c r="T47" s="15">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="U47" s="16">
-        <v>2.57</v>
+        <v>1</v>
       </c>
       <c r="V47" s="15">
-        <v>3885</v>
+        <v>1320</v>
       </c>
       <c r="W47" s="15"/>
       <c r="X47" s="15"/>
@@ -18129,37 +18035,37 @@
         <v>1</v>
       </c>
       <c r="Z47" s="20">
-        <v>104.99</v>
+        <v>65.99</v>
       </c>
       <c r="AA47"/>
       <c r="AB47"/>
       <c r="AC47" s="15"/>
       <c r="AD47" s="19">
-        <v>15</v>
+        <v>212</v>
       </c>
       <c r="AE47" s="15">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AF47" s="21">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AG47" s="22">
-        <v>0.3514</v>
+        <v>0.1</v>
       </c>
       <c r="AH47" s="20">
-        <v>5.46</v>
+        <v>8.68</v>
       </c>
       <c r="AI47" s="16">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="AJ47"/>
       <c r="AK47" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2024-12-29</t>
         </is>
       </c>
       <c r="AL47" s="19">
-        <v>61</v>
+        <v>648</v>
       </c>
       <c r="AM47" s="13" t="inlineStr">
         <is>
@@ -18177,7 +18083,7 @@
       </c>
       <c r="AS47" s="14" t="inlineStr">
         <is>
-          <t>EUROAPEX LANDING</t>
+          <t>GreatStarTools</t>
         </is>
       </c>
       <c r="AT47" s="13" t="inlineStr">
@@ -18187,17 +18093,17 @@
       </c>
       <c r="AU47" s="13" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV47" s="14" t="inlineStr">
         <is>
-          <t>DOLNOŚLĄSKIE 53-332 PL</t>
+          <t>Shangcheng Zhejiang 310019 CN</t>
         </is>
       </c>
       <c r="AW47" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ABSTVEQNNON26</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1H05RYQWRY6GC</t>
         </is>
       </c>
       <c r="AX47" s="13"/>
@@ -18222,47 +18128,47 @@
       <c r="BI47" s="23"/>
       <c r="BJ47" s="23" t="inlineStr">
         <is>
-          <t>4 kg</t>
+          <t>5,48 Kilograms</t>
         </is>
       </c>
       <c r="BK47" s="23" t="inlineStr">
         <is>
-          <t>4.00 kg</t>
+          <t>5.48 kg</t>
         </is>
       </c>
       <c r="BL47" s="23" t="inlineStr">
         <is>
-          <t>43 x 19 x 32 cm</t>
+          <t>17.3 x 32.6 x 30.6 cm</t>
         </is>
       </c>
       <c r="BM47" s="23" t="inlineStr">
         <is>
-          <t>43.00 x 19.00 x 32.00 cm</t>
+          <t>17.30 x 32.60 x 30.60 cm</t>
         </is>
       </c>
       <c r="BN47" s="23" t="inlineStr">
         <is>
-          <t>4.67 kg</t>
+          <t>5.48 kg</t>
         </is>
       </c>
       <c r="BO47" s="23" t="inlineStr">
         <is>
-          <t>4.67 kg</t>
+          <t>5.48 kg</t>
         </is>
       </c>
       <c r="BP47" s="23" t="inlineStr">
         <is>
-          <t>45 x 31.5 x 19.9 cm</t>
+          <t>39.6 x 34.3 x 20 cm</t>
         </is>
       </c>
       <c r="BQ47" s="23" t="inlineStr">
         <is>
-          <t>45.00 x 31.50 x 19.90 cm</t>
+          <t>39.60 x 34.30 x 20.00 cm</t>
         </is>
       </c>
       <c r="BR47" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -18273,40 +18179,40 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B086Q46MMD</t>
+          <t>B0G8ZCQP4L</t>
         </is>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>STANHOME</t>
+          <t>ICARE</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/STANHOME/page/CF140807-E9D9-4EE4-98E8-28F83571D17F?lp_asin=B086Q46MMD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.it/stores/ICARE/page/683C743F-F13A-445C-9854-23FD69D4559D?lp_asin=B0G8ZCQP4L&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>STANHOMEsDetergente Smacchiante Tappeti Carpet Cleaner, 500 ML, Pulisce e Smacchia i Tessuti d'Arredamento</t>
+          <t>ICARE 600W Lavatappeti Portatile - lavatappeti - 1,5L lava tappezzeria ad Acqua - Lava, Asciuga e Aspira 3 in 1 - Ideale per</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B086Q46MMD?psc=1</t>
+          <t>https://www.amazon.it/dp/B0G8ZCQP4L?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31hUTFxCzpL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41lsfPHzIUL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B086Q46MMD</t>
+          <t>B0G8ZCQP4L</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
@@ -18320,13 +18226,13 @@
         </is>
       </c>
       <c r="O48" s="15">
-        <v>10119</v>
+        <v>20553</v>
       </c>
       <c r="P48" s="15">
-        <v>6003</v>
+        <v>495840</v>
       </c>
       <c r="Q48" s="16">
-        <v>0.44</v>
+        <v>0.83</v>
       </c>
       <c r="R48" s="17" t="inlineStr">
         <is>
@@ -18335,164 +18241,152 @@
       </c>
       <c r="S48" s="18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T48" s="15">
-        <v>148</v>
-      </c>
-      <c r="U48" s="16">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U48" s="16"/>
       <c r="V48" s="15">
-        <v>2220</v>
-      </c>
-      <c r="W48" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X48" s="15">
-        <v>750</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="W48" s="15"/>
+      <c r="X48" s="15"/>
       <c r="Y48" s="19">
         <v>1</v>
       </c>
       <c r="Z48" s="20">
-        <v>15</v>
+        <v>79.99</v>
       </c>
       <c r="AA48"/>
       <c r="AB48"/>
       <c r="AC48" s="15"/>
       <c r="AD48" s="19">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="AE48" s="15">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AF48" s="21">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AG48" s="22">
-        <v>0.0473</v>
+        <v>0</v>
       </c>
       <c r="AH48" s="20">
-        <v>3.74</v>
+        <v>8.9</v>
       </c>
       <c r="AI48" s="16">
-        <v>0.6</v>
+        <v>0.74</v>
       </c>
       <c r="AJ48"/>
       <c r="AK48" s="13" t="inlineStr">
         <is>
-          <t>2020-05-09</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AL48" s="19">
-        <v>2343</v>
+        <v>159</v>
       </c>
       <c r="AM48" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN48" s="13"/>
       <c r="AO48" s="13"/>
       <c r="AP48"/>
       <c r="AQ48" s="19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR48" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS48" s="14" t="inlineStr">
         <is>
-          <t>Stanhome S.p.A</t>
+          <t>VIVARALimited</t>
         </is>
       </c>
       <c r="AT48" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU48" s="13" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="AV48" s="14" t="inlineStr">
         <is>
-          <t>ITALIA 25038 IT</t>
+          <t>DUBLIN D01 KF30 IE</t>
         </is>
       </c>
       <c r="AW48" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1FKDALFGWQLQF</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2JKAAX5C9NSN3</t>
         </is>
       </c>
       <c r="AX48" s="13"/>
-      <c r="AY48" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY48" s="13"/>
       <c r="AZ48" s="13"/>
       <c r="BA48" s="13"/>
       <c r="BB48" s="13"/>
-      <c r="BC48" s="13"/>
-      <c r="BD48" s="13"/>
+      <c r="BC48" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD48" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE48" s="13"/>
       <c r="BF48" s="13"/>
       <c r="BG48" s="13"/>
       <c r="BH48" s="14"/>
-      <c r="BI48" s="23" t="inlineStr">
-        <is>
-          <t>Scelta Amazon</t>
-        </is>
-      </c>
+      <c r="BI48" s="23"/>
       <c r="BJ48" s="23" t="inlineStr">
         <is>
-          <t>550 grammi</t>
+          <t>5,33 Kilograms</t>
         </is>
       </c>
       <c r="BK48" s="23" t="inlineStr">
         <is>
-          <t>550.00 g</t>
+          <t>5.33 kg</t>
         </is>
       </c>
       <c r="BL48" s="23" t="inlineStr">
         <is>
-          <t>6,7 x 24 x 6,7 cm</t>
-        </is>
-      </c>
-      <c r="BM48" s="23" t="inlineStr">
-        <is>
-          <t>6.70 x 24.00 x 6.70 cm</t>
-        </is>
-      </c>
+          <t>39P x 19,5l x 34H cm</t>
+        </is>
+      </c>
+      <c r="BM48" s="23"/>
       <c r="BN48" s="23" t="inlineStr">
         <is>
-          <t>550 g</t>
+          <t>5.33 kg</t>
         </is>
       </c>
       <c r="BO48" s="23" t="inlineStr">
         <is>
-          <t>550.00 g</t>
+          <t>5.33 kg</t>
         </is>
       </c>
       <c r="BP48" s="23" t="inlineStr">
         <is>
-          <t>23.7 x 6.1 x 6 cm</t>
+          <t>39.1 x 39 x 20.3 cm</t>
         </is>
       </c>
       <c r="BQ48" s="23" t="inlineStr">
         <is>
-          <t>23.70 x 6.10 x 6.00 cm</t>
+          <t>39.10 x 39.00 x 20.30 cm</t>
         </is>
       </c>
       <c r="BR48" s="13" t="inlineStr">
         <is>
-          <t>超大号信封</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -18503,546 +18397,104 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0D8KZDB13</t>
+          <t>B0FXX9KJ1D</t>
         </is>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
-      <c r="F49" s="14" t="inlineStr">
-        <is>
-          <t>WORKPRO</t>
-        </is>
-      </c>
+      <c r="F49" s="14"/>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/WORKPROCuraOgniDettaglioperLei/page/3671C642-31F6-4DBC-ACA3-01D7F4B6F085?lp_asin=B0D8KZDB13&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.itundefined</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>WORKPRO Lavatappeti Portatile 450W, Lava Tappezzeria, Pulitore Tappezzeria, Ideale per Pulisci Scale, Divano, Sedili Auto, Mo</t>
+          <t>Polti StainOver Pet SC50, Lavatappeti a Vapore per Rimuovere le Macchies2000 W, 4 in 1, Smacchiatore con Funzione Vaporetto</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0D8KZDB13?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FXX9KJ1D?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41preSMoUJL._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51QsiPBPCjL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0D8KZDB13</t>
-        </is>
-      </c>
-      <c r="M49" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Lavatappeti</t>
-        </is>
-      </c>
-      <c r="N49" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e c</t>
-        </is>
-      </c>
-      <c r="O49" s="15">
-        <v>45732</v>
-      </c>
-      <c r="P49" s="15">
-        <v>243255</v>
-      </c>
-      <c r="Q49" s="16">
-        <v>0.89</v>
-      </c>
-      <c r="R49" s="17" t="inlineStr">
-        <is>
-          <t>Lavatappeti</t>
-        </is>
-      </c>
-      <c r="S49" s="18" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="T49" s="15">
-        <v>20</v>
-      </c>
-      <c r="U49" s="16">
-        <v>1</v>
-      </c>
-      <c r="V49" s="15">
-        <v>1320</v>
-      </c>
+          <t>B0FXX9KJ1D</t>
+        </is>
+      </c>
+      <c r="M49" s="14"/>
+      <c r="N49" s="14"/>
+      <c r="O49" s="15"/>
+      <c r="P49" s="15"/>
+      <c r="Q49" s="16"/>
+      <c r="R49" s="17"/>
+      <c r="S49" s="18"/>
+      <c r="T49" s="15"/>
+      <c r="U49" s="16"/>
+      <c r="V49" s="15"/>
       <c r="W49" s="15"/>
       <c r="X49" s="15"/>
-      <c r="Y49" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z49" s="20">
-        <v>65.99</v>
-      </c>
+      <c r="Y49" s="19"/>
+      <c r="Z49" s="20"/>
       <c r="AA49"/>
       <c r="AB49"/>
       <c r="AC49" s="15"/>
       <c r="AD49" s="19">
-        <v>212</v>
-      </c>
-      <c r="AE49" s="15">
-        <v>2</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="AE49" s="15"/>
       <c r="AF49" s="21">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AG49" s="22">
-        <v>0.1</v>
-      </c>
-      <c r="AH49" s="20">
-        <v>8.68</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH49" s="20"/>
       <c r="AI49" s="16">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="AJ49"/>
-      <c r="AK49" s="13" t="inlineStr">
-        <is>
-          <t>2024-12-29</t>
-        </is>
-      </c>
-      <c r="AL49" s="19">
-        <v>648</v>
-      </c>
-      <c r="AM49" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
+      <c r="AK49" s="13"/>
+      <c r="AL49" s="19"/>
+      <c r="AM49" s="13"/>
       <c r="AN49" s="13"/>
       <c r="AO49" s="13"/>
       <c r="AP49"/>
-      <c r="AQ49" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR49" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS49" s="14" t="inlineStr">
-        <is>
-          <t>GreatStarTools</t>
-        </is>
-      </c>
-      <c r="AT49" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU49" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV49" s="14" t="inlineStr">
-        <is>
-          <t>Shangcheng Zhejiang 310019 CN</t>
-        </is>
-      </c>
-      <c r="AW49" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1H05RYQWRY6GC</t>
-        </is>
-      </c>
+      <c r="AQ49" s="19"/>
+      <c r="AR49" s="19"/>
+      <c r="AS49" s="14"/>
+      <c r="AT49" s="13"/>
+      <c r="AU49" s="13"/>
+      <c r="AV49" s="14"/>
+      <c r="AW49" s="13"/>
       <c r="AX49" s="13"/>
       <c r="AY49" s="13"/>
       <c r="AZ49" s="13"/>
       <c r="BA49" s="13"/>
       <c r="BB49" s="13"/>
-      <c r="BC49" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD49" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC49" s="13"/>
+      <c r="BD49" s="13"/>
       <c r="BE49" s="13"/>
       <c r="BF49" s="13"/>
       <c r="BG49" s="13"/>
       <c r="BH49" s="14"/>
       <c r="BI49" s="23"/>
-      <c r="BJ49" s="23" t="inlineStr">
-        <is>
-          <t>5,48 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK49" s="23" t="inlineStr">
-        <is>
-          <t>5.48 kg</t>
-        </is>
-      </c>
-      <c r="BL49" s="23" t="inlineStr">
-        <is>
-          <t>17.3 x 32.6 x 30.6 cm</t>
-        </is>
-      </c>
-      <c r="BM49" s="23" t="inlineStr">
-        <is>
-          <t>17.30 x 32.60 x 30.60 cm</t>
-        </is>
-      </c>
-      <c r="BN49" s="23" t="inlineStr">
-        <is>
-          <t>5.48 kg</t>
-        </is>
-      </c>
-      <c r="BO49" s="23" t="inlineStr">
-        <is>
-          <t>5.48 kg</t>
-        </is>
-      </c>
-      <c r="BP49" s="23" t="inlineStr">
-        <is>
-          <t>39.6 x 34.3 x 20 cm</t>
-        </is>
-      </c>
-      <c r="BQ49" s="23" t="inlineStr">
-        <is>
-          <t>39.60 x 34.30 x 20.00 cm</t>
-        </is>
-      </c>
-      <c r="BR49" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="13">
-        <v>49</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>B0G8ZCQP4L</t>
-        </is>
-      </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>ICARE</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/stores/ICARE/page/683C743F-F13A-445C-9854-23FD69D4559D?lp_asin=B0G8ZCQP4L&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>ICARE 600W Lavatappeti Portatile - lavatappeti - 1,5L lava tappezzeria ad Acqua - Lava, Asciuga e Aspira 3 in 1 - Ideale per</t>
-        </is>
-      </c>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0G8ZCQP4L?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="14" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/41lsfPHzIUL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="14" t="inlineStr">
-        <is>
-          <t>B0G8ZCQP4L</t>
-        </is>
-      </c>
-      <c r="M50" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Lavatappeti</t>
-        </is>
-      </c>
-      <c r="N50" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e c</t>
-        </is>
-      </c>
-      <c r="O50" s="15">
-        <v>20553</v>
-      </c>
-      <c r="P50" s="15">
-        <v>495840</v>
-      </c>
-      <c r="Q50" s="16">
-        <v>0.83</v>
-      </c>
-      <c r="R50" s="17" t="inlineStr">
-        <is>
-          <t>Lavatappeti</t>
-        </is>
-      </c>
-      <c r="S50" s="18" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="T50" s="15">
-        <v>1</v>
-      </c>
-      <c r="U50" s="16"/>
-      <c r="V50" s="15">
-        <v>80</v>
-      </c>
-      <c r="W50" s="15"/>
-      <c r="X50" s="15"/>
-      <c r="Y50" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z50" s="20">
-        <v>79.99</v>
-      </c>
-      <c r="AA50"/>
-      <c r="AB50"/>
-      <c r="AC50" s="15"/>
-      <c r="AD50" s="19">
-        <v>34</v>
-      </c>
-      <c r="AE50" s="15">
-        <v>18</v>
-      </c>
-      <c r="AF50" s="21">
-        <v>4.3</v>
-      </c>
-      <c r="AG50" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH50" s="20">
-        <v>8.9</v>
-      </c>
-      <c r="AI50" s="16">
-        <v>0.74</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="AL50" s="19">
-        <v>159</v>
-      </c>
-      <c r="AM50" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AN50" s="13"/>
-      <c r="AO50" s="13"/>
-      <c r="AP50"/>
-      <c r="AQ50" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR50" s="19">
-        <v>3</v>
-      </c>
-      <c r="AS50" s="14" t="inlineStr">
-        <is>
-          <t>VIVARALimited</t>
-        </is>
-      </c>
-      <c r="AT50" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU50" s="13" t="inlineStr">
-        <is>
-          <t>IE</t>
-        </is>
-      </c>
-      <c r="AV50" s="14" t="inlineStr">
-        <is>
-          <t>DUBLIN D01 KF30 IE</t>
-        </is>
-      </c>
-      <c r="AW50" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2JKAAX5C9NSN3</t>
-        </is>
-      </c>
-      <c r="AX50" s="13"/>
-      <c r="AY50" s="13"/>
-      <c r="AZ50" s="13"/>
-      <c r="BA50" s="13"/>
-      <c r="BB50" s="13"/>
-      <c r="BC50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE50" s="13"/>
-      <c r="BF50" s="13"/>
-      <c r="BG50" s="13"/>
-      <c r="BH50" s="14"/>
-      <c r="BI50" s="23"/>
-      <c r="BJ50" s="23" t="inlineStr">
-        <is>
-          <t>5,33 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK50" s="23" t="inlineStr">
-        <is>
-          <t>5.33 kg</t>
-        </is>
-      </c>
-      <c r="BL50" s="23" t="inlineStr">
-        <is>
-          <t>39P x 19,5l x 34H cm</t>
-        </is>
-      </c>
-      <c r="BM50" s="23"/>
-      <c r="BN50" s="23" t="inlineStr">
-        <is>
-          <t>5.33 kg</t>
-        </is>
-      </c>
-      <c r="BO50" s="23" t="inlineStr">
-        <is>
-          <t>5.33 kg</t>
-        </is>
-      </c>
-      <c r="BP50" s="23" t="inlineStr">
-        <is>
-          <t>39.1 x 39 x 20.3 cm</t>
-        </is>
-      </c>
-      <c r="BQ50" s="23" t="inlineStr">
-        <is>
-          <t>39.10 x 39.00 x 20.30 cm</t>
-        </is>
-      </c>
-      <c r="BR50" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0FXX9KJ1D</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.itundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>Polti StainOver Pet SC50, Lavatappeti a Vapore per Rimuovere le Macchies2000 W, 4 in 1, Smacchiatore con Funzione Vaporetto</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0FXX9KJ1D?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51QsiPBPCjL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0FXX9KJ1D</t>
-        </is>
-      </c>
-      <c r="M51" s="14"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="19"/>
-      <c r="Z51" s="20"/>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="15"/>
-      <c r="AD51" s="19">
-        <v>17</v>
-      </c>
-      <c r="AE51" s="15"/>
-      <c r="AF51" s="21">
-        <v>3.8</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="20"/>
-      <c r="AI51" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13"/>
-      <c r="AL51" s="19"/>
-      <c r="AM51" s="13"/>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="19"/>
-      <c r="AR51" s="19"/>
-      <c r="AS51" s="14"/>
-      <c r="AT51" s="13"/>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13"/>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23"/>
-      <c r="BJ51" s="23"/>
-      <c r="BK51" s="23"/>
-      <c r="BL51" s="23"/>
-      <c r="BM51" s="23"/>
-      <c r="BN51" s="23"/>
-      <c r="BO51" s="23"/>
-      <c r="BP51" s="23"/>
-      <c r="BQ51" s="23"/>
-      <c r="BR51" s="13"/>
+      <c r="BJ49" s="23"/>
+      <c r="BK49" s="23"/>
+      <c r="BL49" s="23"/>
+      <c r="BM49" s="23"/>
+      <c r="BN49" s="23"/>
+      <c r="BO49" s="23"/>
+      <c r="BP49" s="23"/>
+      <c r="BQ49" s="23"/>
+      <c r="BR49" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19377,58 +18829,43 @@
     <hyperlink ref="M45" r:id="rId327" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N45" r:id="rId328"/>
     <hyperlink ref="AW45" r:id="rId329" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A31SIRX8J8S4P9"/>
-    <hyperlink ref="C46" r:id="rId330" tooltip="https://www.amazon.it/dp/B0753NXDPR"/>
-    <hyperlink ref="G46" r:id="rId331" tooltip="https://www.amazon.it/stores/BISSELL/page/EDA95B6C-7064-466B-BACA-347C73A9A423?lp_asin=B0753NXDPR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J46" r:id="rId332" tooltip="https://www.amazon.it/dp/B0753NXDPR?psc=1"/>
-    <hyperlink ref="K46" r:id="rId333" tooltip="https://images-na.ssl-images-amazon.com/images/I/51L21EY2IeL._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId334" tooltip="https://www.amazon.it/dp/B0753NXDPR"/>
+    <hyperlink ref="C46" r:id="rId330" tooltip="https://www.amazon.it/dp/B0H3KVMBCH"/>
+    <hyperlink ref="G46" r:id="rId331" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=MELLWIN"/>
+    <hyperlink ref="J46" r:id="rId332" tooltip="https://www.amazon.it/dp/B0H3KVMBCH?psc=1"/>
+    <hyperlink ref="K46" r:id="rId333" tooltip="https://images-na.ssl-images-amazon.com/images/I/71J+7Vw8QSL._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId334" tooltip="https://www.amazon.it/dp/B0H3KVMBCH"/>
     <hyperlink ref="M46" r:id="rId335" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N46" r:id="rId336"/>
-    <hyperlink ref="C47" r:id="rId337" tooltip="https://www.amazon.it/dp/B0H3KVMBCH"/>
-    <hyperlink ref="G47" r:id="rId338" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=MELLWIN"/>
-    <hyperlink ref="J47" r:id="rId339" tooltip="https://www.amazon.it/dp/B0H3KVMBCH?psc=1"/>
-    <hyperlink ref="K47" r:id="rId340" tooltip="https://images-na.ssl-images-amazon.com/images/I/71J+7Vw8QSL._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId341" tooltip="https://www.amazon.it/dp/B0H3KVMBCH"/>
-    <hyperlink ref="M47" r:id="rId342" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N47" r:id="rId343"/>
-    <hyperlink ref="AW47" r:id="rId344" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ABSTVEQNNON26"/>
-    <hyperlink ref="C48" r:id="rId345" tooltip="https://www.amazon.it/dp/B086Q46MMD"/>
-    <hyperlink ref="G48" r:id="rId346" tooltip="https://www.amazon.it/stores/STANHOME/page/CF140807-E9D9-4EE4-98E8-28F83571D17F?lp_asin=B086Q46MMD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J48" r:id="rId347" tooltip="https://www.amazon.it/dp/B086Q46MMD?psc=1"/>
-    <hyperlink ref="K48" r:id="rId348" tooltip="https://m.media-amazon.com/images/I/31hUTFxCzpL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId349" tooltip="https://www.amazon.it/dp/B086Q46MMD"/>
-    <hyperlink ref="M48" r:id="rId350" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N48" r:id="rId351"/>
-    <hyperlink ref="AW48" r:id="rId352" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1FKDALFGWQLQF"/>
-    <hyperlink ref="C49" r:id="rId353" tooltip="https://www.amazon.it/dp/B0D8KZDB13"/>
-    <hyperlink ref="G49" r:id="rId354" tooltip="https://www.amazon.it/stores/WORKPROCuraOgniDettaglioperLei/page/3671C642-31F6-4DBC-ACA3-01D7F4B6F085?lp_asin=B0D8KZDB13&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J49" r:id="rId355" tooltip="https://www.amazon.it/dp/B0D8KZDB13?psc=1"/>
-    <hyperlink ref="K49" r:id="rId356" tooltip="https://m.media-amazon.com/images/I/41preSMoUJL._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId357" tooltip="https://www.amazon.it/dp/B0D8KZDB13"/>
-    <hyperlink ref="M49" r:id="rId358" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N49" r:id="rId359"/>
-    <hyperlink ref="AW49" r:id="rId360" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1H05RYQWRY6GC"/>
-    <hyperlink ref="C50" r:id="rId361" tooltip="https://www.amazon.it/dp/B0G8ZCQP4L"/>
-    <hyperlink ref="G50" r:id="rId362" tooltip="https://www.amazon.it/stores/ICARE/page/683C743F-F13A-445C-9854-23FD69D4559D?lp_asin=B0G8ZCQP4L&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J50" r:id="rId363" tooltip="https://www.amazon.it/dp/B0G8ZCQP4L?psc=1"/>
-    <hyperlink ref="K50" r:id="rId364" tooltip="https://m.media-amazon.com/images/I/41lsfPHzIUL._AC_US600_.jpg"/>
-    <hyperlink ref="L50" r:id="rId365" tooltip="https://www.amazon.it/dp/B0G8ZCQP4L"/>
-    <hyperlink ref="M50" r:id="rId366" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N50" r:id="rId367"/>
-    <hyperlink ref="AW50" r:id="rId368" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2JKAAX5C9NSN3"/>
-    <hyperlink ref="C51" r:id="rId369" tooltip="https://www.amazon.it/dp/B0FXX9KJ1D"/>
-    <hyperlink ref="G51" r:id="rId370" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J51" r:id="rId371" tooltip="https://www.amazon.it/dp/B0FXX9KJ1D?psc=1"/>
-    <hyperlink ref="K51" r:id="rId372" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51QsiPBPCjL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId373" tooltip="https://www.amazon.it/dp/B0FXX9KJ1D"/>
+    <hyperlink ref="AW46" r:id="rId337" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ABSTVEQNNON26"/>
+    <hyperlink ref="C47" r:id="rId338" tooltip="https://www.amazon.it/dp/B0D8KZDB13"/>
+    <hyperlink ref="G47" r:id="rId339" tooltip="https://www.amazon.it/stores/WORKPROCuraOgniDettaglioperLei/page/3671C642-31F6-4DBC-ACA3-01D7F4B6F085?lp_asin=B0D8KZDB13&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J47" r:id="rId340" tooltip="https://www.amazon.it/dp/B0D8KZDB13?psc=1"/>
+    <hyperlink ref="K47" r:id="rId341" tooltip="https://m.media-amazon.com/images/I/41preSMoUJL._AC_US600_.jpg"/>
+    <hyperlink ref="L47" r:id="rId342" tooltip="https://www.amazon.it/dp/B0D8KZDB13"/>
+    <hyperlink ref="M47" r:id="rId343" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N47" r:id="rId344"/>
+    <hyperlink ref="AW47" r:id="rId345" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1H05RYQWRY6GC"/>
+    <hyperlink ref="C48" r:id="rId346" tooltip="https://www.amazon.it/dp/B0G8ZCQP4L"/>
+    <hyperlink ref="G48" r:id="rId347" tooltip="https://www.amazon.it/stores/ICARE/page/683C743F-F13A-445C-9854-23FD69D4559D?lp_asin=B0G8ZCQP4L&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J48" r:id="rId348" tooltip="https://www.amazon.it/dp/B0G8ZCQP4L?psc=1"/>
+    <hyperlink ref="K48" r:id="rId349" tooltip="https://m.media-amazon.com/images/I/41lsfPHzIUL._AC_US600_.jpg"/>
+    <hyperlink ref="L48" r:id="rId350" tooltip="https://www.amazon.it/dp/B0G8ZCQP4L"/>
+    <hyperlink ref="M48" r:id="rId351" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N48" r:id="rId352"/>
+    <hyperlink ref="AW48" r:id="rId353" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2JKAAX5C9NSN3"/>
+    <hyperlink ref="C49" r:id="rId354" tooltip="https://www.amazon.it/dp/B0FXX9KJ1D"/>
+    <hyperlink ref="G49" r:id="rId355" tooltip="https://www.amazon.itundefined"/>
+    <hyperlink ref="J49" r:id="rId356" tooltip="https://www.amazon.it/dp/B0FXX9KJ1D?psc=1"/>
+    <hyperlink ref="K49" r:id="rId357" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51QsiPBPCjL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L49" r:id="rId358" tooltip="https://www.amazon.it/dp/B0FXX9KJ1D"/>
   </hyperlinks>
-  <drawing r:id="rId374"/>
+  <drawing r:id="rId359"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -19481,18 +18918,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>5389</v>
+        <v>5046</v>
       </c>
       <c r="C2" s="15">
-        <v>591357</v>
+        <v>586215</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>109.73408795694934</v>
+        <v>116.17419738406659</v>
       </c>
       <c r="G2" s="22">
-        <v>0.413584036838066</v>
+        <v>0.40242443576042747</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19513,7 +18950,7 @@
         <v>88.420245398773</v>
       </c>
       <c r="G3" s="22">
-        <v>0.12509593246354567</v>
+        <v>0.1299944174176569</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19534,7 +18971,7 @@
         <v>107.88512911843277</v>
       </c>
       <c r="G4" s="22">
-        <v>0.0861857252494244</v>
+        <v>0.08956057101842252</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19555,7 +18992,7 @@
         <v>217.11764705882354</v>
       </c>
       <c r="G5" s="22">
-        <v>0.02478894858019954</v>
+        <v>0.02575962995454183</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19576,7 +19013,7 @@
         <v>58.63019250253293</v>
       </c>
       <c r="G6" s="22">
-        <v>0.07574827321565618</v>
+        <v>0.0787144110375628</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19597,7 +19034,7 @@
         <v>117.6395061728395</v>
       </c>
       <c r="G7" s="22">
-        <v>0.03108211818879509</v>
+        <v>0.0322992264135896</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19618,7 +19055,7 @@
         <v>185.96666666666667</v>
       </c>
       <c r="G8" s="22">
-        <v>0.01841903300076746</v>
+        <v>0.019140282319164207</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19639,7 +19076,7 @@
         <v>125.95223880597015</v>
       </c>
       <c r="G9" s="22">
-        <v>0.025709900230237913</v>
+        <v>0.02671664407050004</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19660,7 +19097,7 @@
         <v>106.38144329896907</v>
       </c>
       <c r="G10" s="22">
-        <v>0.022333077513430544</v>
+        <v>0.023207592311986602</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19681,7 +19118,7 @@
         <v>65.99092970521542</v>
       </c>
       <c r="G11" s="22">
-        <v>0.03384497313891021</v>
+        <v>0.03517026876146423</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19702,7 +19139,7 @@
         <v>199.993006993007</v>
       </c>
       <c r="G12" s="22">
-        <v>0.010974673829623945</v>
+        <v>0.011404418215168674</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19723,7 +19160,7 @@
         <v>67.89090909090909</v>
       </c>
       <c r="G13" s="22">
-        <v>0.02532617037605526</v>
+        <v>0.026317888188850787</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19744,7 +19181,7 @@
         <v>109.98989898989899</v>
       </c>
       <c r="G14" s="22">
-        <v>0.015195702225633155</v>
+        <v>0.01579073291331047</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19765,7 +19202,7 @@
         <v>79.98841698841699</v>
       </c>
       <c r="G15" s="22">
-        <v>0.01987720644666155</v>
+        <v>0.020655554669431374</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19786,7 +19223,7 @@
         <v>145.67142857142858</v>
       </c>
       <c r="G16" s="22">
-        <v>0.010744435917114352</v>
+        <v>0.01116516468617912</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19807,7 +19244,7 @@
         <v>63.050909090909094</v>
       </c>
       <c r="G17" s="22">
-        <v>0.02110514198004605</v>
+        <v>0.021931573490708987</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19828,7 +19265,7 @@
         <v>119.9921875</v>
       </c>
       <c r="G18" s="22">
-        <v>0.009823484267075978</v>
+        <v>0.010208150570220911</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19849,7 +19286,7 @@
         <v>130.0</v>
       </c>
       <c r="G19" s="22">
-        <v>0.003760552570990023</v>
+        <v>0.003907807640162692</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19870,7 +19307,7 @@
         <v>74.68493150684931</v>
       </c>
       <c r="G20" s="22">
-        <v>0.005602455871066769</v>
+        <v>0.005821835872079113</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19891,7 +19328,7 @@
         <v>79.9076923076923</v>
       </c>
       <c r="G21" s="22">
-        <v>0.0049884881043745204</v>
+        <v>0.005183826461440306</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19912,88 +19349,67 @@
         <v>105.0</v>
       </c>
       <c r="G22" s="22">
-        <v>0.00283960092095165</v>
+        <v>0.002950793524204482</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>STANHOME</t>
+          <t>WORKPRO</t>
         </is>
       </c>
       <c r="B23" s="15">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="C23" s="15">
-        <v>2220</v>
+        <v>1320</v>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="15"/>
       <c r="F23" s="20">
-        <v>15.0</v>
+        <v>66.0</v>
       </c>
       <c r="G23" s="22">
-        <v>0.0113584036838066</v>
+        <v>0.0015950235265970174</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>WORKPRO</t>
+          <t>ICARE</t>
         </is>
       </c>
       <c r="B24" s="15">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C24" s="15">
-        <v>1320</v>
+        <v>80</v>
       </c>
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
       <c r="F24" s="20">
-        <v>66.0</v>
+        <v>80.0</v>
       </c>
       <c r="G24" s="22">
-        <v>0.0015349194167306216</v>
+        <v>7.975117632985087e-05</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>ICARE</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B25" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" s="15">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
-      <c r="F25" s="20">
-        <v>80.0</v>
-      </c>
+      <c r="F25" s="20"/>
       <c r="G25" s="22">
-        <v>7.674597083653108e-05</v>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B26" s="15">
-        <v>0</v>
-      </c>
-      <c r="C26" s="15">
-        <v>0</v>
-      </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="22">
         <v>0.0</v>
       </c>
     </row>
@@ -20005,7 +19421,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -20058,18 +19474,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>8997</v>
+        <v>8654</v>
       </c>
       <c r="C2" s="15">
-        <v>960558</v>
+        <v>955416</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>106.76425475158386</v>
+        <v>110.4016639704183</v>
       </c>
       <c r="G2" s="22">
-        <v>0.6904834996162701</v>
+        <v>0.6901666799585294</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20090,7 +19506,7 @@
         <v>58.63019250253293</v>
       </c>
       <c r="G3" s="22">
-        <v>0.07574827321565618</v>
+        <v>0.0787144110375628</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20111,7 +19527,7 @@
         <v>117.6395061728395</v>
       </c>
       <c r="G4" s="22">
-        <v>0.03108211818879509</v>
+        <v>0.0322992264135896</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20132,7 +19548,7 @@
         <v>189.98969072164948</v>
       </c>
       <c r="G5" s="22">
-        <v>0.01488871834228703</v>
+        <v>0.015471728207991068</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20153,7 +19569,7 @@
         <v>512.695652173913</v>
       </c>
       <c r="G6" s="22">
-        <v>0.005295471987720644</v>
+        <v>0.00550283116675971</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20174,7 +19590,7 @@
         <v>106.38144329896907</v>
       </c>
       <c r="G7" s="22">
-        <v>0.022333077513430544</v>
+        <v>0.023207592311986602</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20195,7 +19611,7 @@
         <v>157.5904255319149</v>
       </c>
       <c r="G8" s="22">
-        <v>0.014428242517267844</v>
+        <v>0.014993221150011962</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20216,7 +19632,7 @@
         <v>65.99092970521542</v>
       </c>
       <c r="G9" s="22">
-        <v>0.03384497313891021</v>
+        <v>0.03517026876146423</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20237,7 +19653,7 @@
         <v>67.89090909090909</v>
       </c>
       <c r="G10" s="22">
-        <v>0.02532617037605526</v>
+        <v>0.026317888188850787</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20258,7 +19674,7 @@
         <v>109.98989898989899</v>
       </c>
       <c r="G11" s="22">
-        <v>0.015195702225633155</v>
+        <v>0.01579073291331047</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20279,7 +19695,7 @@
         <v>69.99126637554585</v>
       </c>
       <c r="G12" s="22">
-        <v>0.01757482732156562</v>
+        <v>0.01826301937953585</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20300,7 +19716,7 @@
         <v>119.9921875</v>
       </c>
       <c r="G13" s="22">
-        <v>0.009823484267075978</v>
+        <v>0.010208150570220911</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20321,7 +19737,7 @@
         <v>85.48979591836735</v>
       </c>
       <c r="G14" s="22">
-        <v>0.011281657712970069</v>
+        <v>0.011723422920488077</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20342,7 +19758,7 @@
         <v>99.992</v>
       </c>
       <c r="G15" s="22">
-        <v>0.009593246354566385</v>
+        <v>0.009968897041231358</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20363,7 +19779,7 @@
         <v>169.0</v>
       </c>
       <c r="G16" s="22">
-        <v>0.0035303146584804296</v>
+        <v>0.00366855411117314</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20384,7 +19800,7 @@
         <v>130.0</v>
       </c>
       <c r="G17" s="22">
-        <v>0.003760552570990023</v>
+        <v>0.003907807640162692</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20405,88 +19821,67 @@
         <v>105.0</v>
       </c>
       <c r="G18" s="22">
-        <v>0.00283960092095165</v>
+        <v>0.002950793524204482</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>Stanhome S.p.A</t>
+          <t>GreatStarTools</t>
         </is>
       </c>
       <c r="B19" s="15">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="C19" s="15">
-        <v>2220</v>
+        <v>1320</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="20">
-        <v>15.0</v>
+        <v>66.0</v>
       </c>
       <c r="G19" s="22">
-        <v>0.0113584036838066</v>
+        <v>0.0015950235265970174</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>GreatStarTools</t>
+          <t>VIVARALimited</t>
         </is>
       </c>
       <c r="B20" s="15">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C20" s="15">
-        <v>1320</v>
+        <v>80</v>
       </c>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="20">
-        <v>66.0</v>
+        <v>80.0</v>
       </c>
       <c r="G20" s="22">
-        <v>0.0015349194167306216</v>
+        <v>7.975117632985087e-05</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>VIVARALimited</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B21" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" s="15">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
-      <c r="F21" s="20">
-        <v>80.0</v>
-      </c>
+      <c r="F21" s="20"/>
       <c r="G21" s="22">
-        <v>7.674597083653108e-05</v>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B22" s="15">
-        <v>0</v>
-      </c>
-      <c r="C22" s="15">
-        <v>0</v>
-      </c>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="22">
         <v>0.0</v>
       </c>
     </row>
